--- a/Experiences/Mesures brutes colle 2.xlsx
+++ b/Experiences/Mesures brutes colle 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\Mines IC\TR Fluide\VS\Experiences\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6A508DC-DDA1-4AF0-BFE9-0C71D055AF6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7419FBC-5B96-470F-9992-88F7DFCFF65F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{AD7160A8-CAF6-4368-9CC5-AF41EE04A10E}"/>
   </bookViews>
@@ -90,9 +90,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -409,6 +410,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5318C3AF-0075-4797-B196-BA8BE1B4CA10}">
   <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="6" max="6" width="7.1796875" customWidth="1"/>
+    <col min="7" max="7" width="7.453125" customWidth="1"/>
+    <col min="8" max="8" width="7.1796875" customWidth="1"/>
+    <col min="9" max="9" width="7.81640625" customWidth="1"/>
+    <col min="10" max="10" width="7.90625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -447,7 +455,7 @@
         <v>9.5000000000000005E-5</v>
       </c>
       <c r="B2" s="1">
-        <v>2.0000000000000002E-5</v>
+        <v>0.02</v>
       </c>
       <c r="C2">
         <v>9.6300000000000008</v>
@@ -458,19 +466,19 @@
       <c r="E2" s="1">
         <v>1270</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2" s="2">
         <v>15</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="2">
         <v>90</v>
       </c>
-      <c r="H2" s="1">
+      <c r="H2" s="2">
         <v>0.4</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2" s="2">
         <v>907</v>
       </c>
-      <c r="J2" s="1">
+      <c r="J2" s="2">
         <v>9.81</v>
       </c>
       <c r="L2" s="1"/>
@@ -480,7 +488,7 @@
         <v>9.5000000000000005E-5</v>
       </c>
       <c r="B3" s="1">
-        <v>5.0000000000000002E-5</v>
+        <v>0.05</v>
       </c>
       <c r="C3">
         <v>10.32</v>
@@ -491,19 +499,19 @@
       <c r="E3" s="1">
         <v>1270</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3" s="2">
         <v>15</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" s="2">
         <v>90</v>
       </c>
-      <c r="H3" s="1">
+      <c r="H3" s="2">
         <v>0.4</v>
       </c>
-      <c r="I3" s="1">
+      <c r="I3" s="2">
         <v>907</v>
       </c>
-      <c r="J3" s="1">
+      <c r="J3" s="2">
         <v>9.81</v>
       </c>
     </row>
@@ -512,7 +520,7 @@
         <v>9.5000000000000005E-5</v>
       </c>
       <c r="B4" s="1">
-        <v>1E-4</v>
+        <v>0.1</v>
       </c>
       <c r="C4">
         <v>9.91</v>
@@ -523,19 +531,19 @@
       <c r="E4" s="1">
         <v>1270</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4" s="2">
         <v>15</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" s="2">
         <v>90</v>
       </c>
-      <c r="H4" s="1">
+      <c r="H4" s="2">
         <v>0.4</v>
       </c>
-      <c r="I4" s="1">
+      <c r="I4" s="2">
         <v>907</v>
       </c>
-      <c r="J4" s="1">
+      <c r="J4" s="2">
         <v>9.81</v>
       </c>
     </row>
@@ -544,7 +552,7 @@
         <v>5.5000000000000002E-5</v>
       </c>
       <c r="B5" s="1">
-        <v>2.0000000000000002E-5</v>
+        <v>0.02</v>
       </c>
       <c r="C5">
         <v>8.39</v>
@@ -555,19 +563,19 @@
       <c r="E5" s="1">
         <v>1270</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="2">
         <v>15</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" s="2">
         <v>90</v>
       </c>
-      <c r="H5" s="1">
+      <c r="H5" s="2">
         <v>0.4</v>
       </c>
-      <c r="I5" s="1">
+      <c r="I5" s="2">
         <v>907</v>
       </c>
-      <c r="J5" s="1">
+      <c r="J5" s="2">
         <v>9.81</v>
       </c>
     </row>
@@ -576,7 +584,7 @@
         <v>5.5000000000000002E-5</v>
       </c>
       <c r="B6" s="1">
-        <v>5.0000000000000002E-5</v>
+        <v>0.05</v>
       </c>
       <c r="C6">
         <v>8.6300000000000008</v>
@@ -587,19 +595,19 @@
       <c r="E6" s="1">
         <v>1270</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="2">
         <v>15</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" s="2">
         <v>90</v>
       </c>
-      <c r="H6" s="1">
+      <c r="H6" s="2">
         <v>0.4</v>
       </c>
-      <c r="I6" s="1">
+      <c r="I6" s="2">
         <v>907</v>
       </c>
-      <c r="J6" s="1">
+      <c r="J6" s="2">
         <v>9.81</v>
       </c>
     </row>
@@ -608,7 +616,7 @@
         <v>5.5000000000000002E-5</v>
       </c>
       <c r="B7" s="1">
-        <v>1E-4</v>
+        <v>0.1</v>
       </c>
       <c r="C7">
         <v>8.3000000000000007</v>
@@ -619,19 +627,19 @@
       <c r="E7" s="1">
         <v>1270</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="2">
         <v>15</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" s="2">
         <v>90</v>
       </c>
-      <c r="H7" s="1">
+      <c r="H7" s="2">
         <v>0.4</v>
       </c>
-      <c r="I7" s="1">
+      <c r="I7" s="2">
         <v>907</v>
       </c>
-      <c r="J7" s="1">
+      <c r="J7" s="2">
         <v>9.81</v>
       </c>
     </row>
@@ -640,7 +648,7 @@
         <v>5.5000000000000002E-5</v>
       </c>
       <c r="B8" s="1">
-        <v>2.0000000000000001E-4</v>
+        <v>0.2</v>
       </c>
       <c r="C8">
         <v>8.36</v>
@@ -651,19 +659,19 @@
       <c r="E8" s="1">
         <v>1270</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="2">
         <v>15</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" s="2">
         <v>90</v>
       </c>
-      <c r="H8" s="1">
+      <c r="H8" s="2">
         <v>0.4</v>
       </c>
-      <c r="I8" s="1">
+      <c r="I8" s="2">
         <v>907</v>
       </c>
-      <c r="J8" s="1">
+      <c r="J8" s="2">
         <v>9.81</v>
       </c>
     </row>

--- a/Experiences/Mesures brutes colle 2.xlsx
+++ b/Experiences/Mesures brutes colle 2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\Mines IC\TR Fluide\VS\Experiences\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7419FBC-5B96-470F-9992-88F7DFCFF65F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A12B906-E5A4-4CE8-AADD-C03618B68E9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{AD7160A8-CAF6-4368-9CC5-AF41EE04A10E}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="19420" windowHeight="10300" xr2:uid="{AD7160A8-CAF6-4368-9CC5-AF41EE04A10E}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="13">
   <si>
     <t>m [kg]</t>
   </si>
@@ -55,6 +55,15 @@
   </si>
   <si>
     <t>g</t>
+  </si>
+  <si>
+    <t>matériau</t>
+  </si>
+  <si>
+    <t>colle</t>
+  </si>
+  <si>
+    <t>t_final [s]</t>
   </si>
 </sst>
 </file>
@@ -90,10 +99,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -408,270 +416,325 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5318C3AF-0075-4797-B196-BA8BE1B4CA10}">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="6" max="6" width="7.1796875" customWidth="1"/>
-    <col min="7" max="7" width="7.453125" customWidth="1"/>
     <col min="8" max="8" width="7.1796875" customWidth="1"/>
-    <col min="9" max="9" width="7.81640625" customWidth="1"/>
-    <col min="10" max="10" width="7.90625" customWidth="1"/>
+    <col min="9" max="9" width="7.453125" customWidth="1"/>
+    <col min="10" max="10" width="7.1796875" customWidth="1"/>
+    <col min="11" max="11" width="7.81640625" customWidth="1"/>
+    <col min="12" max="12" width="7.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" s="1">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2">
+        <f>90*60</f>
+        <v>5400</v>
+      </c>
+      <c r="C2" s="1">
         <v>9.5000000000000005E-5</v>
       </c>
-      <c r="B2" s="1">
+      <c r="D2" s="1">
         <v>0.02</v>
       </c>
-      <c r="C2">
+      <c r="E2">
         <v>9.6300000000000008</v>
       </c>
-      <c r="D2">
+      <c r="F2">
         <v>18.850000000000001</v>
       </c>
-      <c r="E2" s="1">
+      <c r="G2" s="1">
         <v>1270</v>
       </c>
-      <c r="F2" s="2">
+      <c r="H2">
         <v>15</v>
       </c>
-      <c r="G2" s="2">
+      <c r="I2">
         <v>90</v>
       </c>
-      <c r="H2" s="2">
+      <c r="J2">
         <v>0.4</v>
       </c>
-      <c r="I2" s="2">
-        <v>907</v>
-      </c>
-      <c r="J2" s="2">
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
         <v>9.81</v>
       </c>
-      <c r="L2" s="1"/>
+      <c r="N2" s="1"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="1">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3">
+        <f t="shared" ref="B3:B8" si="0">90*60</f>
+        <v>5400</v>
+      </c>
+      <c r="C3" s="1">
         <v>9.5000000000000005E-5</v>
       </c>
-      <c r="B3" s="1">
+      <c r="D3" s="1">
         <v>0.05</v>
       </c>
-      <c r="C3">
+      <c r="E3">
         <v>10.32</v>
       </c>
-      <c r="D3">
+      <c r="F3">
         <v>22.71</v>
       </c>
-      <c r="E3" s="1">
+      <c r="G3" s="1">
         <v>1270</v>
       </c>
-      <c r="F3" s="2">
+      <c r="H3">
         <v>15</v>
       </c>
-      <c r="G3" s="2">
+      <c r="I3">
         <v>90</v>
       </c>
-      <c r="H3" s="2">
+      <c r="J3">
         <v>0.4</v>
       </c>
-      <c r="I3" s="2">
-        <v>907</v>
-      </c>
-      <c r="J3" s="2">
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
         <v>9.81</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="1">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4">
+        <f t="shared" si="0"/>
+        <v>5400</v>
+      </c>
+      <c r="C4" s="1">
         <v>9.5000000000000005E-5</v>
       </c>
-      <c r="B4" s="1">
+      <c r="D4" s="1">
         <v>0.1</v>
       </c>
-      <c r="C4">
+      <c r="E4">
         <v>9.91</v>
       </c>
-      <c r="D4">
+      <c r="F4">
         <v>24.91</v>
       </c>
-      <c r="E4" s="1">
+      <c r="G4" s="1">
         <v>1270</v>
       </c>
-      <c r="F4" s="2">
+      <c r="H4">
         <v>15</v>
       </c>
-      <c r="G4" s="2">
+      <c r="I4">
         <v>90</v>
       </c>
-      <c r="H4" s="2">
+      <c r="J4">
         <v>0.4</v>
       </c>
-      <c r="I4" s="2">
-        <v>907</v>
-      </c>
-      <c r="J4" s="2">
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
         <v>9.81</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5" s="1">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <f t="shared" si="0"/>
+        <v>5400</v>
+      </c>
+      <c r="C5" s="1">
         <v>5.5000000000000002E-5</v>
       </c>
-      <c r="B5" s="1">
+      <c r="D5" s="1">
         <v>0.02</v>
       </c>
-      <c r="C5">
+      <c r="E5">
         <v>8.39</v>
       </c>
-      <c r="D5">
+      <c r="F5">
         <v>16.79</v>
       </c>
-      <c r="E5" s="1">
+      <c r="G5" s="1">
         <v>1270</v>
       </c>
-      <c r="F5" s="2">
+      <c r="H5">
         <v>15</v>
       </c>
-      <c r="G5" s="2">
+      <c r="I5">
         <v>90</v>
       </c>
-      <c r="H5" s="2">
+      <c r="J5">
         <v>0.4</v>
       </c>
-      <c r="I5" s="2">
-        <v>907</v>
-      </c>
-      <c r="J5" s="2">
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
         <v>9.81</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A6" s="1">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6">
+        <f t="shared" si="0"/>
+        <v>5400</v>
+      </c>
+      <c r="C6" s="1">
         <v>5.5000000000000002E-5</v>
       </c>
-      <c r="B6" s="1">
+      <c r="D6" s="1">
         <v>0.05</v>
       </c>
-      <c r="C6">
+      <c r="E6">
         <v>8.6300000000000008</v>
       </c>
-      <c r="D6">
+      <c r="F6">
         <v>18.579999999999998</v>
       </c>
-      <c r="E6" s="1">
+      <c r="G6" s="1">
         <v>1270</v>
       </c>
-      <c r="F6" s="2">
+      <c r="H6">
         <v>15</v>
       </c>
-      <c r="G6" s="2">
+      <c r="I6">
         <v>90</v>
       </c>
-      <c r="H6" s="2">
+      <c r="J6">
         <v>0.4</v>
       </c>
-      <c r="I6" s="2">
-        <v>907</v>
-      </c>
-      <c r="J6" s="2">
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
         <v>9.81</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A7" s="1">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <f t="shared" si="0"/>
+        <v>5400</v>
+      </c>
+      <c r="C7" s="1">
         <v>5.5000000000000002E-5</v>
       </c>
-      <c r="B7" s="1">
+      <c r="D7" s="1">
         <v>0.1</v>
       </c>
-      <c r="C7">
+      <c r="E7">
         <v>8.3000000000000007</v>
       </c>
-      <c r="D7">
+      <c r="F7">
         <v>21.69</v>
       </c>
-      <c r="E7" s="1">
+      <c r="G7" s="1">
         <v>1270</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7">
         <v>15</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7">
         <v>90</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7">
         <v>0.4</v>
       </c>
-      <c r="I7" s="2">
-        <v>907</v>
-      </c>
-      <c r="J7" s="2">
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
         <v>9.81</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A8" s="1">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8">
+        <f t="shared" si="0"/>
+        <v>5400</v>
+      </c>
+      <c r="C8" s="1">
         <v>5.5000000000000002E-5</v>
       </c>
-      <c r="B8" s="1">
+      <c r="D8" s="1">
         <v>0.2</v>
       </c>
-      <c r="C8">
+      <c r="E8">
         <v>8.36</v>
       </c>
-      <c r="D8">
+      <c r="F8">
         <v>23.67</v>
       </c>
-      <c r="E8" s="1">
+      <c r="G8" s="1">
         <v>1270</v>
       </c>
-      <c r="F8" s="2">
+      <c r="H8">
         <v>15</v>
       </c>
-      <c r="G8" s="2">
+      <c r="I8">
         <v>90</v>
       </c>
-      <c r="H8" s="2">
+      <c r="J8">
         <v>0.4</v>
       </c>
-      <c r="I8" s="2">
-        <v>907</v>
-      </c>
-      <c r="J8" s="2">
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
         <v>9.81</v>
       </c>
     </row>
